--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Auto Post\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE00C52-6960-4E7F-8069-671533334245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D628A49F-CC46-4CF5-9180-207502BF4357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="2310" windowWidth="21600" windowHeight="13170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
   <si>
     <t>ID</t>
   </si>
@@ -107,12 +107,6 @@
   </si>
   <si>
     <t>videos/sw1.mp4</t>
-  </si>
-  <si>
-    <t>31-07-2025  15:50:00 PM</t>
-  </si>
-  <si>
-    <t>31-07-2025  15:51:00 PM</t>
   </si>
 </sst>
 </file>
@@ -594,8 +588,8 @@
       <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>26</v>
+      <c r="E2" s="4">
+        <v>45870.111111111109</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>10</v>
@@ -616,8 +610,8 @@
       <c r="D3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>27</v>
+      <c r="E3" s="8">
+        <v>45870.111805555556</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>10</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Auto Post\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55CAB20B-732E-40B5-8345-61B15A0A31A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74AAC67-468D-46AB-8CC2-069D6BFBF398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="2310" windowWidth="21600" windowHeight="13170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -589,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="4">
-        <v>46235.125</v>
+        <v>46234.899305555555</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>10</v>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="8">
-        <v>46235.125694444447</v>
+        <v>46234.899305555555</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>10</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Auto Post\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74AAC67-468D-46AB-8CC2-069D6BFBF398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC14A4D-9D7E-4759-B531-7F5F6C2F3D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="2310" windowWidth="21600" windowHeight="13170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -589,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="4">
-        <v>46234.899305555555</v>
+        <v>46235.136805555558</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>10</v>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="8">
-        <v>46234.899305555555</v>
+        <v>46235.137499999997</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>10</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Auto Post\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC14A4D-9D7E-4759-B531-7F5F6C2F3D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{667C90D7-AD40-4EDA-94F6-88A2BC90E137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="2310" windowWidth="21600" windowHeight="13170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -589,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="4">
-        <v>46235.136805555558</v>
+        <v>46235.140277777777</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>10</v>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="8">
-        <v>46235.137499999997</v>
+        <v>46235.140972222223</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>10</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Auto Post\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF125FC-2045-4468-BE77-9A68E386EE98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0669B054-C4F6-4E33-9175-D9C9C3F9B75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="2310" windowWidth="21600" windowHeight="13170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -589,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="4">
-        <v>46235.147222222222</v>
+        <v>46235.151388888888</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>10</v>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="8">
-        <v>46235.147916666669</v>
+        <v>46235.151388888888</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>10</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Auto Post\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0669B054-C4F6-4E33-9175-D9C9C3F9B75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E99BA55-7FBC-4AEB-915E-0217890E9CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="2310" windowWidth="21600" windowHeight="13170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -589,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="4">
-        <v>46235.151388888888</v>
+        <v>46235.154166666667</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>10</v>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="8">
-        <v>46235.151388888888</v>
+        <v>46235.154166666667</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>10</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Auto Post\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E99BA55-7FBC-4AEB-915E-0217890E9CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EDA702-88E3-4CD2-8714-F6762739D0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="2310" windowWidth="21600" windowHeight="13170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -589,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="4">
-        <v>46235.154166666667</v>
+        <v>46235.125</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>10</v>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="8">
-        <v>46235.154166666667</v>
+        <v>46235.125</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>10</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Auto Post\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2B3EB9-0A73-460A-ADEF-552B54EBCDD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B0201BA-1494-42C8-9383-E5CE410DC86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="2310" windowWidth="21600" windowHeight="13170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9570" yWindow="1410" windowWidth="21600" windowHeight="13170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Content Calendar" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
   <si>
     <t>ID</t>
   </si>
@@ -107,12 +107,6 @@
   </si>
   <si>
     <t>videos/sw1.mp4</t>
-  </si>
-  <si>
-    <t>01-08-2026  13:05:00 PM</t>
-  </si>
-  <si>
-    <t>01-08-2026  13:06:00 PM</t>
   </si>
 </sst>
 </file>
@@ -594,8 +588,8 @@
       <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>26</v>
+      <c r="E2" s="4">
+        <v>46235.555555555555</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>10</v>
@@ -616,8 +610,8 @@
       <c r="D3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>27</v>
+      <c r="E3" s="8">
+        <v>46235.555555555555</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>10</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Auto Post\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA59E75-BC06-4032-AC0F-CA36DE36BB78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071BB7F1-2582-4D51-B078-8CF7C00352AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5355" yWindow="2310" windowWidth="21600" windowHeight="13170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -576,7 +576,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="4">
-        <v>46236.694444444445</v>
+        <v>46236.704861111109</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>11</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\Sublime - Nirupama\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94B2FB6-5E3F-42D2-8577-CF94407502C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35309A7-C8A2-4F4A-9B63-4E78CF6AA3F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -575,7 +575,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="4">
-        <v>46258.857638888891</v>
+        <v>46258.863194444442</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>8</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2884,9 +2884,14 @@
       <c r="E77" s="7" t="n">
         <v>46259.8125</v>
       </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F77" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1062499286531952</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2917,9 +2917,14 @@
       <c r="E78" s="7" t="n">
         <v>46259.90625</v>
       </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F78" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1062577216524159</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -700,9 +700,14 @@
       <c r="E4" s="7" t="n">
         <v>46259.96875</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2162004791023961</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\Sublime - Nirupama\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C295456C-FD2E-4FB7-B9DA-F29AF99B91E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC4BD3F-46B1-462B-BC8E-D3EB8B1F1593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1414,7 +1414,7 @@
         <v>46262.034722222219</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I10" s="5"/>
     </row>
@@ -2974,7 +2974,7 @@
         <v>163</v>
       </c>
       <c r="E84" s="9">
-        <v>46262.045138888891</v>
+        <v>46278.8125</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>20</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -963,9 +963,14 @@
       <c r="E12" s="7" t="n">
         <v>46262.26041666666</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1378869520862302</t>
         </is>
       </c>
       <c r="I12" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3100,9 +3100,14 @@
       <c r="E85" s="9" t="n">
         <v>46262.30208333334</v>
       </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1064600196321861</t>
         </is>
       </c>
       <c r="I85" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3134,9 +3134,14 @@
       <c r="E86" s="9" t="n">
         <v>46262.8125</v>
       </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1065066426275238</t>
         </is>
       </c>
       <c r="I86" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3168,9 +3168,14 @@
       <c r="E87" s="9" t="n">
         <v>46262.90625</v>
       </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1065164009598813</t>
         </is>
       </c>
       <c r="I87" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -997,9 +997,14 @@
       <c r="E13" s="7" t="n">
         <v>46262.96875</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1806117290803293</t>
         </is>
       </c>
       <c r="I13" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1031,9 +1031,14 @@
       <c r="E14" s="7" t="n">
         <v>46263.11458333334</v>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1826891048469695</t>
         </is>
       </c>
       <c r="I14" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1065,9 +1065,14 @@
       <c r="E15" s="7" t="n">
         <v>46263.26041666666</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1050105684322064</t>
         </is>
       </c>
       <c r="I15" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3217,9 +3217,14 @@
       <c r="E88" s="9" t="n">
         <v>46263.30208333334</v>
       </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1065471546234726</t>
         </is>
       </c>
       <c r="I88" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3251,9 +3251,14 @@
       <c r="E89" s="9" t="n">
         <v>46263.8125</v>
       </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1065916872856860</t>
         </is>
       </c>
       <c r="I89" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3285,9 +3285,14 @@
       <c r="E90" s="9" t="n">
         <v>46263.90625</v>
       </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F90" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1066014522847095</t>
         </is>
       </c>
       <c r="I90" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3319,9 +3319,14 @@
       <c r="E91" s="9" t="n">
         <v>46264.30208333334</v>
       </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1066323089482905</t>
         </is>
       </c>
       <c r="I91" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3353,9 +3353,14 @@
       <c r="E92" s="9" t="n">
         <v>46264.8125</v>
       </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1066768982771649</t>
         </is>
       </c>
       <c r="I92" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3387,9 +3387,14 @@
       <c r="E93" s="9" t="n">
         <v>46264.90625</v>
       </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1066869399428274</t>
         </is>
       </c>
       <c r="I93" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3421,9 +3421,14 @@
       <c r="E94" s="9" t="n">
         <v>46265.30208333334</v>
       </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F94" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1067167529398461</t>
         </is>
       </c>
       <c r="I94" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3455,9 +3455,14 @@
       <c r="E95" s="9" t="n">
         <v>46265.8125</v>
       </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F95" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>1067590079356206</t>
         </is>
       </c>
       <c r="I95" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3489,9 +3489,14 @@
       <c r="E96" s="9" t="n">
         <v>46265.90625</v>
       </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>1067685239346690</t>
         </is>
       </c>
       <c r="I96" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3542,9 +3542,14 @@
       <c r="E97" s="9" t="n">
         <v>46266.30208333334</v>
       </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F97" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1067989965982884</t>
         </is>
       </c>
       <c r="I97" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3576,9 +3576,14 @@
       <c r="E98" s="9" t="n">
         <v>46266.8125</v>
       </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F98" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1068461952602352</t>
         </is>
       </c>
       <c r="I98" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3610,9 +3610,14 @@
       <c r="E99" s="9" t="n">
         <v>46266.90625</v>
       </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F99" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1068559152592632</t>
         </is>
       </c>
       <c r="I99" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1379,9 +1379,14 @@
       <c r="E25" s="7" t="n">
         <v>46266.96875</v>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2603709180083212</t>
         </is>
       </c>
       <c r="I25" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1413,9 +1413,14 @@
       <c r="E26" s="7" t="n">
         <v>46267.11458333334</v>
       </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2080729296168190</t>
         </is>
       </c>
       <c r="I26" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1447,9 +1447,14 @@
       <c r="E27" s="7" t="n">
         <v>46267.26041666666</v>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>965145043269596</t>
         </is>
       </c>
       <c r="I27" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3659,9 +3659,14 @@
       <c r="E100" s="9" t="n">
         <v>46267.30208333334</v>
       </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F100" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1068876592560888</t>
         </is>
       </c>
       <c r="I100" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3693,9 +3693,14 @@
       <c r="E101" s="9" t="n">
         <v>46267.8125</v>
       </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F101" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>1069304329184781</t>
         </is>
       </c>
       <c r="I101" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3727,9 +3727,14 @@
       <c r="E102" s="9" t="n">
         <v>46267.90625</v>
       </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F102" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1069396029175611</t>
         </is>
       </c>
       <c r="I102" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1481,9 +1481,14 @@
       <c r="E28" s="7" t="n">
         <v>46267.96875</v>
       </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1410043661221637</t>
         </is>
       </c>
       <c r="I28" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1515,9 +1515,14 @@
       <c r="E29" s="7" t="n">
         <v>46268.11458333334</v>
       </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1757636092053437</t>
         </is>
       </c>
       <c r="I29" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1549,9 +1549,14 @@
       <c r="E30" s="7" t="n">
         <v>46268.26041666666</v>
       </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1320096560200960</t>
         </is>
       </c>
       <c r="I30" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3776,9 +3776,14 @@
       <c r="E103" s="9" t="n">
         <v>46268.30208333334</v>
       </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F103" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>1069700269145187</t>
         </is>
       </c>
       <c r="I103" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3810,9 +3810,14 @@
       <c r="E104" s="9" t="n">
         <v>46268.8125</v>
       </c>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F104" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>1070182515763629</t>
         </is>
       </c>
       <c r="I104" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3844,9 +3844,14 @@
       <c r="E105" s="9" t="n">
         <v>46268.90625</v>
       </c>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F105" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>1070276869087527</t>
         </is>
       </c>
       <c r="I105" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1583,9 +1583,14 @@
       <c r="E31" s="7" t="n">
         <v>46268.96875</v>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1820056872327596</t>
         </is>
       </c>
       <c r="I31" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1617,9 +1617,14 @@
       <c r="E32" s="7" t="n">
         <v>46269.11458333334</v>
       </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1720757155853750</t>
         </is>
       </c>
       <c r="I32" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1651,9 +1651,14 @@
       <c r="E33" s="7" t="n">
         <v>46269.26041666666</v>
       </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>963934230068007</t>
         </is>
       </c>
       <c r="I33" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3893,9 +3893,14 @@
       <c r="E106" s="9" t="n">
         <v>46269.30208333334</v>
       </c>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F106" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>1070593562389191</t>
         </is>
       </c>
       <c r="I106" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3927,9 +3927,14 @@
       <c r="E107" s="9" t="n">
         <v>46269.8125</v>
       </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F107" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>1071059985675882</t>
         </is>
       </c>
       <c r="I107" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3961,9 +3961,14 @@
       <c r="E108" s="9" t="n">
         <v>46269.90625</v>
       </c>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F108" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>1071162652332282</t>
         </is>
       </c>
       <c r="I108" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1685,9 +1685,14 @@
       <c r="E34" s="7" t="n">
         <v>46269.96875</v>
       </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1778546896671562</t>
         </is>
       </c>
       <c r="I34" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1719,9 +1719,14 @@
       <c r="E35" s="7" t="n">
         <v>46270.11458333334</v>
       </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1593116655586911</t>
         </is>
       </c>
       <c r="I35" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1753,9 +1753,14 @@
       <c r="E36" s="7" t="n">
         <v>46270.26041666666</v>
       </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1071679615404553</t>
         </is>
       </c>
       <c r="I36" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4010,9 +4010,14 @@
       <c r="E109" s="9" t="n">
         <v>46270.30208333334</v>
       </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F109" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>1071501972298350</t>
         </is>
       </c>
       <c r="I109" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4044,9 +4044,14 @@
       <c r="E110" s="9" t="n">
         <v>46270.8125</v>
       </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F110" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1071970442251503</t>
         </is>
       </c>
       <c r="I110" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4078,9 +4078,14 @@
       <c r="E111" s="9" t="n">
         <v>46270.90625</v>
       </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F111" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1072070305574850</t>
         </is>
       </c>
       <c r="I111" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1787,9 +1787,14 @@
       <c r="E37" s="7" t="n">
         <v>46270.96875</v>
       </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1437815708409304</t>
         </is>
       </c>
       <c r="I37" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1821,9 +1821,14 @@
       <c r="E38" s="7" t="n">
         <v>46271.11458333334</v>
       </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1091957770184327</t>
         </is>
       </c>
       <c r="I38" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1855,9 +1855,14 @@
       <c r="E39" s="7" t="n">
         <v>46271.26041666666</v>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1068764158871455</t>
         </is>
       </c>
       <c r="I39" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4127,9 +4127,14 @@
       <c r="E112" s="9" t="n">
         <v>46271.30208333334</v>
       </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F112" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>1072402818874932</t>
         </is>
       </c>
       <c r="I112" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4161,9 +4161,14 @@
       <c r="E113" s="9" t="n">
         <v>46271.8125</v>
       </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F113" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1072850158830198</t>
         </is>
       </c>
       <c r="I113" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4195,9 +4195,14 @@
       <c r="E114" s="9" t="n">
         <v>46271.90625</v>
       </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F114" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1072942358820978</t>
         </is>
       </c>
       <c r="I114" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1889,9 +1889,14 @@
       <c r="E40" s="7" t="n">
         <v>46271.96875</v>
       </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F40" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1495364215946124</t>
         </is>
       </c>
       <c r="I40" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1923,9 +1923,14 @@
       <c r="E41" s="7" t="n">
         <v>46272.11458333334</v>
       </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1391264015950408</t>
         </is>
       </c>
       <c r="I41" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1957,9 +1957,14 @@
       <c r="E42" s="7" t="n">
         <v>46272.26041666666</v>
       </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>905917085612419</t>
         </is>
       </c>
       <c r="I42" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4244,9 +4244,14 @@
       <c r="E115" s="9" t="n">
         <v>46272.30208333334</v>
       </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F115" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>1073281358787078</t>
         </is>
       </c>
       <c r="I115" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4278,9 +4278,14 @@
       <c r="E116" s="9" t="n">
         <v>46272.8125</v>
       </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F116" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>1073719592076588</t>
         </is>
       </c>
       <c r="I116" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4312,9 +4312,14 @@
       <c r="E117" s="9" t="n">
         <v>46272.90625</v>
       </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F117" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>1073814162067131</t>
         </is>
       </c>
       <c r="I117" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1991,9 +1991,14 @@
       <c r="E43" s="7" t="n">
         <v>46272.96875</v>
       </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1624203232547924</t>
         </is>
       </c>
       <c r="I43" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2025,9 +2025,14 @@
       <c r="E44" s="7" t="n">
         <v>46273.11458333334</v>
       </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1408281061446827</t>
         </is>
       </c>
       <c r="I44" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2059,9 +2059,14 @@
       <c r="E45" s="7" t="n">
         <v>46273.26041666666</v>
       </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F45" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1371728895125956</t>
         </is>
       </c>
       <c r="I45" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4361,9 +4361,14 @@
       <c r="E118" s="9" t="n">
         <v>46273.30208333334</v>
       </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F118" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1074120015369879</t>
         </is>
       </c>
       <c r="I118" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4395,9 +4395,14 @@
       <c r="E119" s="9" t="n">
         <v>46273.8125</v>
       </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F119" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>1074557358659478</t>
         </is>
       </c>
       <c r="I119" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4429,9 +4429,14 @@
       <c r="E120" s="9" t="n">
         <v>46273.90625</v>
       </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F120" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>1074652988649915</t>
         </is>
       </c>
       <c r="I120" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2093,9 +2093,14 @@
       <c r="E46" s="7" t="n">
         <v>46273.96875</v>
       </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F46" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1402049895226693</t>
         </is>
       </c>
       <c r="I46" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2127,9 +2127,14 @@
       <c r="E47" s="7" t="n">
         <v>46274.11458333334</v>
       </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F47" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1593120918953344</t>
         </is>
       </c>
       <c r="I47" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2161,9 +2161,14 @@
       <c r="E48" s="7" t="n">
         <v>46274.26041666666</v>
       </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1564845774637058</t>
         </is>
       </c>
       <c r="I48" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4478,9 +4478,14 @@
       <c r="E121" s="9" t="n">
         <v>46274.30208333334</v>
       </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F121" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1074958521952695</t>
         </is>
       </c>
       <c r="I121" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4512,9 +4512,14 @@
       <c r="E122" s="9" t="n">
         <v>46274.8125</v>
       </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F122" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>1075404641908083</t>
         </is>
       </c>
       <c r="I122" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4546,9 +4546,14 @@
       <c r="E123" s="9" t="n">
         <v>46274.90625</v>
       </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F123" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>1075501235231757</t>
         </is>
       </c>
       <c r="I123" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2195,9 +2195,14 @@
       <c r="E49" s="7" t="n">
         <v>46274.96875</v>
       </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F49" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1595617898621461</t>
         </is>
       </c>
       <c r="I49" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2229,9 +2229,14 @@
       <c r="E50" s="7" t="n">
         <v>46275.11458333334</v>
       </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F50" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1570766497858389</t>
         </is>
       </c>
       <c r="I50" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2263,9 +2263,14 @@
       <c r="E51" s="7" t="n">
         <v>46275.26041666666</v>
       </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F51" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2091813475060258</t>
         </is>
       </c>
       <c r="I51" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4595,9 +4595,14 @@
       <c r="E124" s="9" t="n">
         <v>46275.30208333334</v>
       </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F124" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>1075808815200999</t>
         </is>
       </c>
       <c r="I124" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4629,9 +4629,14 @@
       <c r="E125" s="9" t="n">
         <v>46275.8125</v>
       </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F125" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>1076288291819718</t>
         </is>
       </c>
       <c r="I125" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4663,9 +4663,14 @@
       <c r="E126" s="9" t="n">
         <v>46275.90625</v>
       </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F126" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>1076388858476328</t>
         </is>
       </c>
       <c r="I126" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2297,9 +2297,14 @@
       <c r="E52" s="7" t="n">
         <v>46275.96875</v>
       </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F52" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1881477889928218</t>
         </is>
       </c>
       <c r="I52" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2331,9 +2331,14 @@
       <c r="E53" s="7" t="n">
         <v>46276.11458333334</v>
       </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F53" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2591177334653713</t>
         </is>
       </c>
       <c r="I53" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2365,9 +2365,14 @@
       <c r="E54" s="7" t="n">
         <v>46276.26041666666</v>
       </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F54" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2106443163292138</t>
         </is>
       </c>
       <c r="I54" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4712,9 +4712,14 @@
       <c r="E127" s="9" t="n">
         <v>46276.30208333334</v>
       </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F127" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>1076702401778307</t>
         </is>
       </c>
       <c r="I127" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4746,9 +4746,14 @@
       <c r="E128" s="9" t="n">
         <v>46276.8125</v>
       </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F128" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>1077153028399911</t>
         </is>
       </c>
       <c r="I128" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3008,9 +3008,14 @@
       <c r="E76" s="7" t="n">
         <v>46276.90625</v>
       </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F76" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1077253231723224</t>
         </is>
       </c>
       <c r="I76" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2399,9 +2399,14 @@
       <c r="E55" s="7" t="n">
         <v>46276.96875</v>
       </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F55" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1561113301834247</t>
         </is>
       </c>
       <c r="I55" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2433,9 +2433,14 @@
       <c r="E56" s="7" t="n">
         <v>46277.11458333334</v>
       </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F56" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1074790191824854</t>
         </is>
       </c>
       <c r="I56" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2467,9 +2467,14 @@
       <c r="E57" s="7" t="n">
         <v>46277.26041666666</v>
       </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F57" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1972117537081253</t>
         </is>
       </c>
       <c r="I57" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3125,9 +3125,14 @@
       <c r="E79" s="9" t="n">
         <v>46277.30208333334</v>
       </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F79" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1077565091692038</t>
         </is>
       </c>
       <c r="I79" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3159,9 +3159,14 @@
       <c r="E80" s="9" t="n">
         <v>46277.8125</v>
       </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F80" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1077996441648903</t>
         </is>
       </c>
       <c r="I80" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3227,9 +3227,14 @@
       <c r="E82" s="9" t="n">
         <v>46277.90625</v>
       </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F82" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1078091898306024</t>
         </is>
       </c>
       <c r="I82" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2501,9 +2501,14 @@
       <c r="E58" s="7" t="n">
         <v>46277.96875</v>
       </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F58" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2534660006997939</t>
         </is>
       </c>
       <c r="I58" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2535,9 +2535,14 @@
       <c r="E59" s="7" t="n">
         <v>46278.11458333334</v>
       </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F59" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1456394443220822</t>
         </is>
       </c>
       <c r="I59" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2569,9 +2569,14 @@
       <c r="E60" s="7" t="n">
         <v>46278.26041666666</v>
       </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F60" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>907513608826305</t>
         </is>
       </c>
       <c r="I60" s="5" t="n"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3276,9 +3276,14 @@
       <c r="E83" s="9" t="n">
         <v>46278.30208333334</v>
       </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F83" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1078413478273866</t>
         </is>
       </c>
       <c r="I83" s="5" t="n"/>
